--- a/app/data/unit_designations.xlsx
+++ b/app/data/unit_designations.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmad Alblooshi\Documents\GitHub\LF_Project\Programming Lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lab\Documents\GitHub\LF_TrainingEvaluationProjrct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C614F4C-2B9C-4644-AC55-1B7A5F2F0A45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D54CCB-F4D3-4981-9020-9E10D7F962CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Units_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Units_Alias" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="301">
   <si>
     <t>الدلالة الرئيسية (الجهة الرسمية)</t>
   </si>
@@ -828,13 +833,109 @@
   </si>
   <si>
     <t>U032</t>
+  </si>
+  <si>
+    <t>U033</t>
+  </si>
+  <si>
+    <t>U034</t>
+  </si>
+  <si>
+    <t>U035</t>
+  </si>
+  <si>
+    <t>U036</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المشاة الراجلة/11</t>
+  </si>
+  <si>
+    <t>كتيبة المشاة الراجلة/11 - السرية/1</t>
+  </si>
+  <si>
+    <t>كتيبة المشاة الراجلة/11 - السرية/2</t>
+  </si>
+  <si>
+    <t>كتيبة المشاة الراجلة/11 - السرية/3</t>
+  </si>
+  <si>
+    <t>قسم الأمن</t>
+  </si>
+  <si>
+    <t>U037</t>
+  </si>
+  <si>
+    <t>A096</t>
+  </si>
+  <si>
+    <t>A097</t>
+  </si>
+  <si>
+    <t>A098</t>
+  </si>
+  <si>
+    <t>A099</t>
+  </si>
+  <si>
+    <t>A100</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>محكم قيادة كتيبة المشاة الراجلة/11</t>
+  </si>
+  <si>
+    <t>محكم قيادة كتيبة/11</t>
+  </si>
+  <si>
+    <t>محكم قيادة الكتيبة/11</t>
+  </si>
+  <si>
+    <t>محكم كتيبة/11</t>
+  </si>
+  <si>
+    <t>محكم الكتيبة/11</t>
+  </si>
+  <si>
+    <t>محكم كتيبة 11</t>
+  </si>
+  <si>
+    <t>محكم الكتيبة 11</t>
+  </si>
+  <si>
+    <t>محكم ك/11</t>
+  </si>
+  <si>
+    <t>محكم قسم الأمن</t>
+  </si>
+  <si>
+    <t>محكم الأمن</t>
+  </si>
+  <si>
+    <t>محكم جماعة الأمن</t>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>A106</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -866,6 +967,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1199,17 +1306,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="25.109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>223</v>
       </c>
@@ -1226,7 +1334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>237</v>
       </c>
@@ -1240,7 +1348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>238</v>
       </c>
@@ -1254,7 +1362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>239</v>
       </c>
@@ -1268,7 +1376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>240</v>
       </c>
@@ -1282,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>241</v>
       </c>
@@ -1296,7 +1404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>242</v>
       </c>
@@ -1310,7 +1418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>243</v>
       </c>
@@ -1324,7 +1432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>244</v>
       </c>
@@ -1338,7 +1446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>245</v>
       </c>
@@ -1352,7 +1460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>246</v>
       </c>
@@ -1366,7 +1474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>247</v>
       </c>
@@ -1380,7 +1488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>248</v>
       </c>
@@ -1394,7 +1502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>249</v>
       </c>
@@ -1408,7 +1516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>250</v>
       </c>
@@ -1422,7 +1530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>251</v>
       </c>
@@ -1436,7 +1544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>252</v>
       </c>
@@ -1450,7 +1558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>253</v>
       </c>
@@ -1464,7 +1572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>254</v>
       </c>
@@ -1478,7 +1586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>255</v>
       </c>
@@ -1492,7 +1600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>256</v>
       </c>
@@ -1506,7 +1614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>257</v>
       </c>
@@ -1520,7 +1628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>258</v>
       </c>
@@ -1534,7 +1642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>259</v>
       </c>
@@ -1548,7 +1656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>260</v>
       </c>
@@ -1562,7 +1670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>261</v>
       </c>
@@ -1576,7 +1684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>262</v>
       </c>
@@ -1590,7 +1698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>263</v>
       </c>
@@ -1604,7 +1712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>264</v>
       </c>
@@ -1618,7 +1726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>265</v>
       </c>
@@ -1632,7 +1740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>266</v>
       </c>
@@ -1646,7 +1754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>267</v>
       </c>
@@ -1660,7 +1768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>268</v>
       </c>
@@ -1674,7 +1782,78 @@
         <v>4</v>
       </c>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1682,16 +1861,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D107"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
@@ -1705,7 +1884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1716,7 +1895,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1727,7 +1906,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1738,7 +1917,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1749,7 +1928,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1760,7 +1939,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1771,7 +1950,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1782,7 +1961,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1793,7 +1972,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1804,7 +1983,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1815,7 +1994,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1826,7 +2005,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1837,7 +2016,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1848,7 +2027,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1859,7 +2038,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1870,7 +2049,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1881,7 +2060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1892,7 +2071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1903,7 +2082,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1914,7 +2093,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1925,7 +2104,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1936,7 +2115,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1947,7 +2126,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1958,7 +2137,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -1969,7 +2148,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -1980,7 +2159,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -1991,7 +2170,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -2002,7 +2181,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2013,7 +2192,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2024,7 +2203,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2035,7 +2214,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -2046,7 +2225,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -2057,7 +2236,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -2068,7 +2247,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -2079,7 +2258,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -2090,7 +2269,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -2101,7 +2280,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2112,7 +2291,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -2123,7 +2302,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -2134,7 +2313,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2324,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2156,7 +2335,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -2167,7 +2346,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2178,7 +2357,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -2189,7 +2368,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -2200,7 +2379,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -2211,7 +2390,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -2222,7 +2401,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -2233,7 +2412,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -2244,7 +2423,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -2255,7 +2434,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -2266,7 +2445,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -2277,7 +2456,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -2288,7 +2467,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -2299,7 +2478,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -2310,7 +2489,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -2321,7 +2500,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -2332,7 +2511,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -2343,7 +2522,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -2354,7 +2533,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>78</v>
       </c>
@@ -2365,7 +2544,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -2376,7 +2555,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -2387,7 +2566,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -2398,7 +2577,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -2409,7 +2588,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2420,7 +2599,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -2431,7 +2610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -2442,7 +2621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -2453,7 +2632,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -2464,7 +2643,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -2475,7 +2654,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -2486,7 +2665,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -2497,7 +2676,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -2508,7 +2687,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -2519,7 +2698,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -2530,7 +2709,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -2541,7 +2720,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -2552,7 +2731,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -2563,7 +2742,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -2574,7 +2753,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -2585,7 +2764,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -2596,7 +2775,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>100</v>
       </c>
@@ -2607,7 +2786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -2618,7 +2797,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -2629,7 +2808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>103</v>
       </c>
@@ -2640,7 +2819,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -2651,7 +2830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>105</v>
       </c>
@@ -2662,7 +2841,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>106</v>
       </c>
@@ -2673,7 +2852,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>107</v>
       </c>
@@ -2684,7 +2863,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>108</v>
       </c>
@@ -2695,7 +2874,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>109</v>
       </c>
@@ -2706,7 +2885,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -2717,7 +2896,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -2728,7 +2907,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>112</v>
       </c>
@@ -2739,7 +2918,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>113</v>
       </c>
@@ -2750,7 +2929,129 @@
         <v>222</v>
       </c>
     </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>280</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C98" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>281</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C99" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>282</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C100" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>283</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C101" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>284</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C102" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>285</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>286</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>287</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>299</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>300</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
